--- a/PhD_working_time_plan.xlsx
+++ b/PhD_working_time_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hauke\Desktop\PhD MPSD Bester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72532AF2-13EE-48A8-B6AB-E6A33A36A104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F752E95D-BE2E-4556-BCDD-6D717FDE4726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="18">
   <si>
     <t xml:space="preserve">Date </t>
   </si>
@@ -61,6 +61,24 @@
   </si>
   <si>
     <t xml:space="preserve">What improve? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes, very productive. But not much Science today. Especially set-up, organizational things  and get to know group. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulare genau durchschauen und durchlesen. Du hast einige MPSD Formulare übersehen. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8h (9-17:30) and after that a bit (0:30h) in evening </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7h (9:30 -17:30) and after that 1 h in the evening </t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes, productive. First real science day. Set-up Chemserv SSH account and first subgroup meeting. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finding an effective way how to get into the topic without feeling stressed when you do the basics. </t>
   </si>
 </sst>
 </file>
@@ -102,9 +120,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -389,7 +410,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6328125" customWidth="1"/>
+    <col min="3" max="3" width="42.7265625" customWidth="1"/>
     <col min="4" max="4" width="33.1796875" customWidth="1"/>
     <col min="5" max="5" width="21.81640625" customWidth="1"/>
   </cols>
@@ -411,25 +432,43 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>46280</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>46281</v>
       </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
         <v>46282</v>
@@ -437,7 +476,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>46283</v>
@@ -445,7 +484,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <v>46284</v>
@@ -453,7 +492,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
         <v>46285</v>
@@ -461,7 +500,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1">
         <v>46286</v>
@@ -469,7 +508,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1">
         <v>46287</v>
@@ -477,7 +516,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1">
         <v>46288</v>
@@ -485,7 +524,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="1">
         <v>46289</v>
@@ -493,7 +532,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="1">
         <v>46290</v>
@@ -501,7 +540,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" s="1">
         <v>46291</v>
@@ -509,7 +548,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1">
         <v>46292</v>
@@ -517,7 +556,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B15" s="1">
         <v>46293</v>
@@ -525,7 +564,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" s="1">
         <v>46294</v>
@@ -533,7 +572,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" s="1">
         <v>46295</v>
@@ -541,7 +580,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" s="1">
         <v>46296</v>
@@ -549,7 +588,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19" s="1">
         <v>46297</v>
@@ -557,7 +596,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20" s="1">
         <v>46298</v>
@@ -565,7 +604,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B21" s="1">
         <v>46299</v>
@@ -573,7 +612,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B22" s="1">
         <v>46300</v>
@@ -581,7 +620,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" s="1">
         <v>46301</v>
@@ -589,7 +628,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" s="1">
         <v>46302</v>
@@ -597,7 +636,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" s="1">
         <v>46303</v>
@@ -605,7 +644,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" s="1">
         <v>46304</v>
@@ -613,7 +652,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" s="1">
         <v>46305</v>
@@ -621,7 +660,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B28" s="1">
         <v>46306</v>
@@ -629,7 +668,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B29" s="1">
         <v>46307</v>
@@ -637,7 +676,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" s="1">
         <v>46308</v>
@@ -645,7 +684,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B31" s="1">
         <v>46309</v>
@@ -653,7 +692,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B32" s="1">
         <v>46310</v>
@@ -661,7 +700,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B33" s="1">
         <v>46311</v>
@@ -669,7 +708,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B34" s="1">
         <v>46312</v>
@@ -677,7 +716,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B35" s="1">
         <v>46313</v>
@@ -685,7 +724,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B36" s="1">
         <v>46314</v>
@@ -693,7 +732,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" s="1">
         <v>46315</v>
@@ -701,7 +740,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" s="1">
         <v>46316</v>
@@ -709,7 +748,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B39" s="1">
         <v>46317</v>
@@ -717,7 +756,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B40" s="1">
         <v>46318</v>
@@ -725,7 +764,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41" s="1">
         <v>46319</v>
@@ -733,7 +772,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B42" s="1">
         <v>46320</v>
@@ -741,7 +780,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B43" s="1">
         <v>46321</v>
@@ -749,7 +788,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" s="1">
         <v>46322</v>
@@ -757,7 +796,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B45" s="1">
         <v>46323</v>
@@ -765,7 +804,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B46" s="1">
         <v>46324</v>
@@ -773,7 +812,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B47" s="1">
         <v>46325</v>
@@ -781,7 +820,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B48" s="1">
         <v>46326</v>
@@ -789,7 +828,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B49" s="1">
         <v>46327</v>
@@ -797,7 +836,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B50" s="1">
         <v>46328</v>
@@ -805,7 +844,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B51" s="1">
         <v>46329</v>
@@ -813,7 +852,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B52" s="1">
         <v>46330</v>
@@ -821,7 +860,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B53" s="1">
         <v>46331</v>
@@ -829,7 +868,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B54" s="1">
         <v>46332</v>
@@ -837,7 +876,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B55" s="1">
         <v>46333</v>
@@ -845,7 +884,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B56" s="1">
         <v>46334</v>
@@ -853,7 +892,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B57" s="1">
         <v>46335</v>
@@ -861,7 +900,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B58" s="1">
         <v>46336</v>
@@ -869,7 +908,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B59" s="1">
         <v>46337</v>
@@ -877,7 +916,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B60" s="1">
         <v>46338</v>
@@ -885,7 +924,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B61" s="1">
         <v>46339</v>
@@ -893,7 +932,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B62" s="1">
         <v>46340</v>
@@ -901,7 +940,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B63" s="1">
         <v>46341</v>
@@ -909,7 +948,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B64" s="1">
         <v>46342</v>
@@ -917,7 +956,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B65" s="1">
         <v>46343</v>
@@ -925,7 +964,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B66" s="1">
         <v>46344</v>
@@ -933,7 +972,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B67" s="1">
         <v>46345</v>
@@ -941,7 +980,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B68" s="1">
         <v>46346</v>
@@ -949,7 +988,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B69" s="1">
         <v>46347</v>
@@ -957,7 +996,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B70" s="1">
         <v>46348</v>
@@ -965,7 +1004,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B71" s="1">
         <v>46349</v>
@@ -973,7 +1012,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" s="1">
         <v>46350</v>
@@ -981,7 +1020,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B73" s="1">
         <v>46351</v>
@@ -989,7 +1028,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B74" s="1">
         <v>46352</v>
@@ -997,7 +1036,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B75" s="1">
         <v>46353</v>
@@ -1005,7 +1044,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B76" s="1">
         <v>46354</v>
@@ -1013,7 +1052,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B77" s="1">
         <v>46355</v>
@@ -1021,7 +1060,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B78" s="1">
         <v>46356</v>
@@ -1029,7 +1068,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B79" s="1">
         <v>46357</v>
@@ -1037,7 +1076,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B80" s="1">
         <v>46358</v>
@@ -1045,7 +1084,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B81" s="1">
         <v>46359</v>
@@ -1053,7 +1092,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B82" s="1">
         <v>46360</v>
@@ -1061,7 +1100,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B83" s="1">
         <v>46361</v>
@@ -1069,7 +1108,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B84" s="1">
         <v>46362</v>
@@ -1077,7 +1116,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B85" s="1">
         <v>46363</v>
@@ -1085,7 +1124,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B86" s="1">
         <v>46364</v>
@@ -1093,7 +1132,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B87" s="1">
         <v>46365</v>
@@ -1101,7 +1140,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B88" s="1">
         <v>46366</v>
@@ -1109,7 +1148,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B89" s="1">
         <v>46367</v>
@@ -1117,7 +1156,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B90" s="1">
         <v>46368</v>
@@ -1125,7 +1164,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B91" s="1">
         <v>46369</v>
@@ -1133,7 +1172,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B92" s="1">
         <v>46370</v>
@@ -1141,7 +1180,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B93" s="1">
         <v>46371</v>
@@ -1149,7 +1188,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B94" s="1">
         <v>46372</v>
@@ -1157,7 +1196,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B95" s="1">
         <v>46373</v>
@@ -1165,7 +1204,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B96" s="1">
         <v>46374</v>
@@ -1173,7 +1212,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B97" s="1">
         <v>46375</v>
@@ -1181,7 +1220,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B98" s="1">
         <v>46376</v>
@@ -1189,7 +1228,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B99" s="1">
         <v>46377</v>
@@ -1197,7 +1236,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B100" s="1">
         <v>46378</v>
@@ -1205,7 +1244,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B101" s="1">
         <v>46379</v>
@@ -1213,7 +1252,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B102" s="1">
         <v>46380</v>
@@ -1221,7 +1260,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B103" s="1">
         <v>46381</v>
@@ -1229,7 +1268,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B104" s="1">
         <v>46382</v>
@@ -1237,7 +1276,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B105" s="1">
         <v>46383</v>
@@ -1245,7 +1284,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B106" s="1">
         <v>46384</v>
@@ -1253,7 +1292,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B107" s="1">
         <v>46385</v>
@@ -1261,7 +1300,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B108" s="1">
         <v>46386</v>
@@ -1269,7 +1308,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B109" s="1">
         <v>46387</v>
@@ -1277,7 +1316,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B110" s="1">
         <v>46388</v>
@@ -1285,7 +1324,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B111" s="1">
         <v>46389</v>
@@ -1293,7 +1332,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B112" s="1">
         <v>46390</v>
@@ -1301,7 +1340,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B113" s="1">
         <v>46391</v>
@@ -1309,7 +1348,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B114" s="1">
         <v>46392</v>
@@ -1317,7 +1356,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B115" s="1">
         <v>46393</v>
@@ -1325,7 +1364,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B116" s="1">
         <v>46394</v>
@@ -1333,7 +1372,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B117" s="1">
         <v>46395</v>
@@ -1341,7 +1380,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B118" s="1">
         <v>46396</v>
@@ -1349,7 +1388,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B119" s="1">
         <v>46397</v>
@@ -1357,7 +1396,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B120" s="1">
         <v>46398</v>
@@ -1365,7 +1404,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B121" s="1">
         <v>46399</v>
@@ -1373,7 +1412,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B122" s="1">
         <v>46400</v>
@@ -1381,7 +1420,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B123" s="1">
         <v>46401</v>
@@ -1389,7 +1428,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B124" s="1">
         <v>46402</v>
@@ -1397,7 +1436,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B125" s="1">
         <v>46403</v>
@@ -1405,7 +1444,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B126" s="1">
         <v>46404</v>
@@ -1413,7 +1452,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B127" s="1">
         <v>46405</v>
@@ -1421,7 +1460,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B128" s="1">
         <v>46406</v>
@@ -1429,7 +1468,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B129" s="1">
         <v>46407</v>
@@ -1437,7 +1476,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B130" s="1">
         <v>46408</v>
@@ -1445,7 +1484,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B131" s="1">
         <v>46409</v>
@@ -1453,7 +1492,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B132" s="1">
         <v>46410</v>
@@ -1461,7 +1500,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B133" s="1">
         <v>46411</v>
@@ -1469,7 +1508,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B134" s="1">
         <v>46412</v>
@@ -1477,7 +1516,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B135" s="1">
         <v>46413</v>
@@ -1485,7 +1524,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B136" s="1">
         <v>46414</v>
@@ -1493,7 +1532,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B137" s="1">
         <v>46415</v>
@@ -1501,7 +1540,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B138" s="1">
         <v>46416</v>
@@ -1509,7 +1548,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B139" s="1">
         <v>46417</v>
@@ -1517,7 +1556,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B140" s="1">
         <v>46418</v>
@@ -1525,7 +1564,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B141" s="1">
         <v>46419</v>
@@ -1533,7 +1572,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B142" s="1">
         <v>46420</v>
@@ -1541,7 +1580,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B143" s="1">
         <v>46421</v>
@@ -1549,7 +1588,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B144" s="1">
         <v>46422</v>
@@ -1557,7 +1596,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B145" s="1">
         <v>46423</v>
@@ -1565,7 +1604,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B146" s="1">
         <v>46424</v>
@@ -1573,7 +1612,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B147" s="1">
         <v>46425</v>
@@ -1581,7 +1620,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B148" s="1">
         <v>46426</v>
@@ -1589,7 +1628,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B149" s="1">
         <v>46427</v>
@@ -1597,7 +1636,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B150" s="1">
         <v>46428</v>
@@ -1605,7 +1644,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B151" s="1">
         <v>46429</v>
@@ -1613,7 +1652,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B152" s="1">
         <v>46430</v>
@@ -1621,7 +1660,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B153" s="1">
         <v>46431</v>
@@ -1629,7 +1668,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B154" s="1">
         <v>46432</v>
@@ -1637,7 +1676,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B155" s="1">
         <v>46433</v>
@@ -1645,7 +1684,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B156" s="1">
         <v>46434</v>
@@ -1653,7 +1692,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B157" s="1">
         <v>46435</v>
@@ -1661,7 +1700,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B158" s="1">
         <v>46436</v>
@@ -1669,7 +1708,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B159" s="1">
         <v>46437</v>
@@ -1677,7 +1716,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B160" s="1">
         <v>46438</v>
@@ -1685,7 +1724,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B161" s="1">
         <v>46439</v>
@@ -1693,7 +1732,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B162" s="1">
         <v>46440</v>
@@ -1701,7 +1740,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B163" s="1">
         <v>46441</v>
@@ -1709,7 +1748,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B164" s="1">
         <v>46442</v>
@@ -1717,7 +1756,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B165" s="1">
         <v>46443</v>
@@ -1725,7 +1764,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B166" s="1">
         <v>46444</v>
@@ -1733,7 +1772,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B167" s="1">
         <v>46445</v>
@@ -1741,7 +1780,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B168" s="1">
         <v>46446</v>
@@ -1749,7 +1788,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B169" s="1">
         <v>46447</v>
@@ -1757,7 +1796,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B170" s="1">
         <v>46448</v>
@@ -1765,7 +1804,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B171" s="1">
         <v>46449</v>
@@ -1773,7 +1812,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B172" s="1">
         <v>46450</v>
@@ -1781,7 +1820,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B173" s="1">
         <v>46451</v>
@@ -1789,7 +1828,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B174" s="1">
         <v>46452</v>
@@ -1797,7 +1836,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B175" s="1">
         <v>46453</v>
@@ -1805,7 +1844,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B176" s="1">
         <v>46454</v>
@@ -1813,7 +1852,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B177" s="1">
         <v>46455</v>
@@ -1821,7 +1860,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B178" s="1">
         <v>46456</v>
@@ -1829,7 +1868,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B179" s="1">
         <v>46457</v>
@@ -1837,7 +1876,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B180" s="1">
         <v>46458</v>
@@ -1845,7 +1884,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B181" s="1">
         <v>46459</v>
@@ -1853,7 +1892,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B182" s="1">
         <v>46460</v>
@@ -1861,7 +1900,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B183" s="1">
         <v>46461</v>
@@ -1869,7 +1908,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B184" s="1">
         <v>46462</v>
@@ -1877,7 +1916,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B185" s="1">
         <v>46463</v>
@@ -1885,7 +1924,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B186" s="1">
         <v>46464</v>
@@ -1893,7 +1932,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B187" s="1">
         <v>46465</v>
@@ -1901,7 +1940,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B188" s="1">
         <v>46466</v>
@@ -1909,7 +1948,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B189" s="1">
         <v>46467</v>
@@ -1917,7 +1956,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B190" s="1">
         <v>46468</v>
@@ -1925,7 +1964,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B191" s="1">
         <v>46469</v>
@@ -1933,7 +1972,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B192" s="1">
         <v>46470</v>
@@ -1941,7 +1980,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B193" s="1">
         <v>46471</v>
@@ -1949,7 +1988,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B194" s="1">
         <v>46472</v>
@@ -1957,7 +1996,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B195" s="1">
         <v>46473</v>
@@ -1965,7 +2004,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B196" s="1">
         <v>46474</v>
@@ -1973,7 +2012,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B197" s="1">
         <v>46475</v>
@@ -1981,7 +2020,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B198" s="1">
         <v>46476</v>
@@ -1989,7 +2028,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B199" s="1">
         <v>46477</v>
@@ -1997,7 +2036,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B200" s="1">
         <v>46478</v>
@@ -2005,7 +2044,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B201" s="1">
         <v>46479</v>
@@ -2013,7 +2052,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B202" s="1">
         <v>46480</v>
@@ -2021,7 +2060,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B203" s="1">
         <v>46481</v>
@@ -2029,7 +2068,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B204" s="1">
         <v>46482</v>
@@ -2037,7 +2076,7 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B205" s="1">
         <v>46483</v>
@@ -2045,7 +2084,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B206" s="1">
         <v>46484</v>
@@ -2053,7 +2092,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B207" s="1">
         <v>46485</v>
@@ -2061,7 +2100,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B208" s="1">
         <v>46486</v>
@@ -2069,7 +2108,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B209" s="1">
         <v>46487</v>
@@ -2077,7 +2116,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B210" s="1">
         <v>46488</v>
@@ -2085,7 +2124,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B211" s="1">
         <v>46489</v>
@@ -2093,7 +2132,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B212" s="1">
         <v>46490</v>
@@ -2101,7 +2140,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B213" s="1">
         <v>46491</v>
@@ -2109,7 +2148,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B214" s="1">
         <v>46492</v>
@@ -2117,7 +2156,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B215" s="1">
         <v>46493</v>
@@ -2125,7 +2164,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B216" s="1">
         <v>46494</v>
@@ -2133,7 +2172,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B217" s="1">
         <v>46495</v>
@@ -2141,7 +2180,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B218" s="1">
         <v>46496</v>
@@ -2149,7 +2188,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B219" s="1">
         <v>46497</v>
@@ -2157,7 +2196,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B220" s="1">
         <v>46498</v>
@@ -2165,7 +2204,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B221" s="1">
         <v>46499</v>
@@ -2173,7 +2212,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B222" s="1">
         <v>46500</v>
@@ -2181,7 +2220,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B223" s="1">
         <v>46501</v>
@@ -2189,7 +2228,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B224" s="1">
         <v>46502</v>
@@ -2197,7 +2236,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B225" s="1">
         <v>46503</v>
@@ -2205,7 +2244,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B226" s="1">
         <v>46504</v>
@@ -2213,7 +2252,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B227" s="1">
         <v>46505</v>
@@ -2221,7 +2260,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B228" s="1">
         <v>46506</v>
@@ -2229,7 +2268,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B229" s="1">
         <v>46507</v>
@@ -2237,7 +2276,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B230" s="1">
         <v>46508</v>
@@ -2245,7 +2284,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B231" s="1">
         <v>46509</v>
@@ -2253,7 +2292,7 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B232" s="1">
         <v>46510</v>
@@ -2261,7 +2300,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B233" s="1">
         <v>46511</v>
@@ -2269,7 +2308,7 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B234" s="1">
         <v>46512</v>
@@ -2277,7 +2316,7 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B235" s="1">
         <v>46513</v>
@@ -2285,7 +2324,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B236" s="1">
         <v>46514</v>
@@ -2293,7 +2332,7 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B237" s="1">
         <v>46515</v>
@@ -2301,7 +2340,7 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B238" s="1">
         <v>46516</v>
@@ -2309,7 +2348,7 @@
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B239" s="1">
         <v>46517</v>
@@ -2317,7 +2356,7 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B240" s="1">
         <v>46518</v>
@@ -2325,7 +2364,7 @@
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B241" s="1">
         <v>46519</v>
@@ -2333,7 +2372,7 @@
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B242" s="1">
         <v>46520</v>
@@ -2341,7 +2380,7 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B243" s="1">
         <v>46521</v>
@@ -2349,7 +2388,7 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B244" s="1">
         <v>46522</v>
@@ -2357,7 +2396,7 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B245" s="1">
         <v>46523</v>
@@ -2365,7 +2404,7 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B246" s="1">
         <v>46524</v>
@@ -2373,7 +2412,7 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B247" s="1">
         <v>46525</v>
@@ -2381,7 +2420,7 @@
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B248" s="1">
         <v>46526</v>
@@ -2389,7 +2428,7 @@
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B249" s="1">
         <v>46527</v>
@@ -2397,7 +2436,7 @@
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B250" s="1">
         <v>46528</v>
@@ -2405,7 +2444,7 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B251" s="1">
         <v>46529</v>
@@ -2413,7 +2452,7 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B252" s="1">
         <v>46530</v>
@@ -2421,7 +2460,7 @@
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B253" s="1">
         <v>46531</v>
@@ -2429,7 +2468,7 @@
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B254" s="1">
         <v>46532</v>
@@ -2437,7 +2476,7 @@
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B255" s="1">
         <v>46533</v>
@@ -2445,7 +2484,7 @@
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B256" s="1">
         <v>46534</v>
@@ -2453,7 +2492,7 @@
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B257" s="1">
         <v>46535</v>
@@ -2461,7 +2500,7 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B258" s="1">
         <v>46536</v>
@@ -2469,7 +2508,7 @@
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B259" s="1">
         <v>46537</v>
@@ -2477,7 +2516,7 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B260" s="1">
         <v>46538</v>
@@ -2485,7 +2524,7 @@
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B261" s="1">
         <v>46539</v>
@@ -2493,7 +2532,7 @@
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B262" s="1">
         <v>46540</v>
@@ -2501,7 +2540,7 @@
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B263" s="1">
         <v>46541</v>
@@ -2509,7 +2548,7 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B264" s="1">
         <v>46542</v>
@@ -2517,7 +2556,7 @@
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B265" s="1">
         <v>46543</v>
@@ -2525,7 +2564,7 @@
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B266" s="1">
         <v>46544</v>
@@ -2533,7 +2572,7 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B267" s="1">
         <v>46545</v>
@@ -2541,7 +2580,7 @@
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B268" s="1">
         <v>46546</v>
@@ -2549,7 +2588,7 @@
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B269" s="1">
         <v>46547</v>
@@ -2557,7 +2596,7 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B270" s="1">
         <v>46548</v>
@@ -2565,7 +2604,7 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B271" s="1">
         <v>46549</v>
@@ -2573,7 +2612,7 @@
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B272" s="1">
         <v>46550</v>
@@ -2581,7 +2620,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B273" s="1">
         <v>46551</v>
@@ -2589,7 +2628,7 @@
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B274" s="1">
         <v>46552</v>
@@ -2597,7 +2636,7 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B275" s="1">
         <v>46553</v>
@@ -2605,7 +2644,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B276" s="1">
         <v>46554</v>
@@ -2613,7 +2652,7 @@
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B277" s="1">
         <v>46555</v>
@@ -2621,7 +2660,7 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B278" s="1">
         <v>46556</v>
@@ -2629,7 +2668,7 @@
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B279" s="1">
         <v>46557</v>
@@ -2637,7 +2676,7 @@
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B280" s="1">
         <v>46558</v>
@@ -2645,7 +2684,7 @@
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B281" s="1">
         <v>46559</v>
@@ -2653,7 +2692,7 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B282" s="1">
         <v>46560</v>
@@ -2661,7 +2700,7 @@
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B283" s="1">
         <v>46561</v>
@@ -2669,7 +2708,7 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B284" s="1">
         <v>46562</v>
@@ -2677,7 +2716,7 @@
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B285" s="1">
         <v>46563</v>
@@ -2685,7 +2724,7 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B286" s="1">
         <v>46564</v>
@@ -2693,7 +2732,7 @@
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B287" s="1">
         <v>46565</v>
@@ -2701,7 +2740,7 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B288" s="1">
         <v>46566</v>

--- a/PhD_working_time_plan.xlsx
+++ b/PhD_working_time_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hauke\Desktop\PhD MPSD Bester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F752E95D-BE2E-4556-BCDD-6D717FDE4726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A57EB-BC2D-4007-BC56-61B7367C7566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="37">
   <si>
     <t xml:space="preserve">Date </t>
   </si>
@@ -79,6 +79,63 @@
   </si>
   <si>
     <t xml:space="preserve">Finding an effective way how to get into the topic without feeling stressed when you do the basics. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6h (9:45 -16:45) and after that 1 h in the evening </t>
+  </si>
+  <si>
+    <t>learn more effectively, drink coffee</t>
+  </si>
+  <si>
+    <t>Much installed. After lunch less productive learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">productive but relaxed day, IMPRS introductory meeting </t>
+  </si>
+  <si>
+    <t>7h (9:45 - 17:45) and after that 1 h in the evening</t>
+  </si>
+  <si>
+    <t>1.5 h am morgen und abend nur</t>
+  </si>
+  <si>
+    <t>finding important papers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1h am morgen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 h (9:30 - 18:30) h </t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes, very long and productive 2h group meeting. Wasted some time with not working ssh keys, around 2 hours. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7h (9:45-17:45) and after that 1h evening </t>
+  </si>
+  <si>
+    <t>surprisingly large difficulties to start simple quantum espressso</t>
+  </si>
+  <si>
+    <t>very productive day generally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6h (10:00 -17:00) </t>
+  </si>
+  <si>
+    <t>2h too litlle worked, after heavy lunch quite tied</t>
+  </si>
+  <si>
+    <t>good smart dialogues with Gabriel and Miguel in lunch break</t>
+  </si>
+  <si>
+    <t>7h30 min 10-18:30 h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very intersting productive day with many crucial papers reading </t>
+  </si>
+  <si>
+    <t>start earlier</t>
   </si>
 </sst>
 </file>
@@ -412,7 +469,7 @@
     <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.7265625" customWidth="1"/>
     <col min="4" max="4" width="33.1796875" customWidth="1"/>
-    <col min="5" max="5" width="21.81640625" customWidth="1"/>
+    <col min="5" max="5" width="32.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -466,21 +523,36 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
         <v>46282</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>46283</v>
       </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -489,6 +561,12 @@
       <c r="B6" s="1">
         <v>46284</v>
       </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -497,37 +575,73 @@
       <c r="B7" s="1">
         <v>46285</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="1">
         <v>46286</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="1">
         <v>46287</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="1">
         <v>46288</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="1">
         <v>46289</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -2749,5 +2863,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/PhD_working_time_plan.xlsx
+++ b/PhD_working_time_plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hauke\Desktop\PhD MPSD Bester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A57EB-BC2D-4007-BC56-61B7367C7566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61339956-A57C-48DE-A6E9-60EF5E9B175D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="69">
   <si>
     <t xml:space="preserve">Date </t>
   </si>
@@ -136,13 +136,109 @@
   </si>
   <si>
     <t>start earlier</t>
+  </si>
+  <si>
+    <t>10:10 -17:10 (6 h) und 23:00 -1:00 nachts 2h</t>
+  </si>
+  <si>
+    <t>finished first reading of dissertation theory chapter</t>
+  </si>
+  <si>
+    <t>0h</t>
+  </si>
+  <si>
+    <t>bureaucracy</t>
+  </si>
+  <si>
+    <t>(7h) 9:30-17:30 und 2h am Abend Docota registration</t>
+  </si>
+  <si>
+    <t>1h emotional diary</t>
+  </si>
+  <si>
+    <t>got running and installed quantum espresso with Franz</t>
+  </si>
+  <si>
+    <t>check together with others before sendig or generating bureaucratic documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">week1 </t>
+  </si>
+  <si>
+    <t>30:00 h worked at 4 days</t>
+  </si>
+  <si>
+    <t>week 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">worked 38:30 h </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7:30 h) 10:10 - 18:40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">quite unproductive although black tea but very nice group meeting and even a small extra meeting for my questio afterwards </t>
+  </si>
+  <si>
+    <t>unrealistische deadlines hinterfragen</t>
+  </si>
+  <si>
+    <t>6:30 h (10:00 - 17:30) h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first time run successfully a quantum espresso script - huge milestone </t>
+  </si>
+  <si>
+    <t>7:00 h (10:00 - 18:00) h</t>
+  </si>
+  <si>
+    <t>done many quantum espresso tutorials</t>
+  </si>
+  <si>
+    <t>8:30 h (10:20-19:50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very productive vim und qe learning and learnt about uhh cloud and apple time machine </t>
+  </si>
+  <si>
+    <t>4h (15-17) h und  (23-1:00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intense Fortran tutorials learning </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1h </t>
+  </si>
+  <si>
+    <t xml:space="preserve">only emotional diary </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR meting and graphene band structure computed with qe from qe tutorials </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 h (9:30 -17:30) h</t>
+  </si>
+  <si>
+    <t>exciton paper reading mainly + PhD seminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8h (9:30 - 18:30) und abends 0.5 h </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5:40 h (10:40 - 17:00)h  </t>
+  </si>
+  <si>
+    <t>very effective learning with Franz together</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,6 +248,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -177,11 +281,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,11 +571,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:E290"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.7265625" customWidth="1"/>
+    <col min="3" max="3" width="49.36328125" customWidth="1"/>
     <col min="4" max="4" width="33.1796875" customWidth="1"/>
     <col min="5" max="5" width="32.54296875" customWidth="1"/>
   </cols>
@@ -579,2284 +687,2387 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1">
         <v>46286</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1">
-        <v>46287</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="1">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1">
+        <v>46288</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1">
         <v>46289</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1">
         <v>46290</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1">
-        <v>46291</v>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1">
-        <v>46292</v>
+        <v>46291</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1">
+        <v>46292</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="1">
         <v>46293</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="1">
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="1">
         <v>46294</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="1">
+      <c r="C18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1">
         <v>46295</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="1">
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1">
         <v>46296</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="1">
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1">
         <v>46297</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="1">
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1">
         <v>46298</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="1">
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1">
         <v>46299</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" s="1">
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="1">
         <v>46300</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="1">
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="1">
         <v>46301</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="1">
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1">
         <v>46302</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="1">
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="1">
         <v>46303</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="1">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="1">
         <v>46304</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="1">
+      <c r="D28" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="1">
         <v>46305</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="1">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1">
         <v>46306</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29" s="1">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="1">
         <v>46307</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="1">
         <v>46308</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="1">
-        <v>46309</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="1">
-        <v>46310</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B33" s="1">
-        <v>46311</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B34" s="1">
-        <v>46312</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B35" s="1">
-        <v>46313</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B36" s="1">
-        <v>46314</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B37" s="1">
-        <v>46315</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B38" s="1">
-        <v>46316</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B39" s="1">
-        <v>46317</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B40" s="1">
-        <v>46318</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B41" s="1">
-        <v>46319</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B42" s="1">
-        <v>46320</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B43" s="1">
-        <v>46321</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B44" s="1">
-        <v>46322</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B45" s="1">
-        <v>46323</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B46" s="1">
-        <v>46324</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B47" s="1">
-        <v>46325</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B48" s="1">
-        <v>46326</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B49" s="1">
-        <v>46327</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B50" s="1">
-        <v>46328</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B51" s="1">
-        <v>46329</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B52" s="1">
-        <v>46330</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B53" s="1">
-        <v>46331</v>
+        <v>46329</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B54" s="1">
-        <v>46332</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B55" s="1">
-        <v>46333</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B56" s="1">
-        <v>46334</v>
+        <v>46332</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B57" s="1">
-        <v>46335</v>
+        <v>46333</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B58" s="1">
-        <v>46336</v>
+        <v>46334</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B59" s="1">
-        <v>46337</v>
+        <v>46335</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B60" s="1">
-        <v>46338</v>
+        <v>46336</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B61" s="1">
-        <v>46339</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B62" s="1">
-        <v>46340</v>
+        <v>46338</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B63" s="1">
-        <v>46341</v>
+        <v>46339</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B64" s="1">
-        <v>46342</v>
+        <v>46340</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B65" s="1">
-        <v>46343</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B66" s="1">
-        <v>46344</v>
+        <v>46342</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B67" s="1">
-        <v>46345</v>
+        <v>46343</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B68" s="1">
-        <v>46346</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B69" s="1">
-        <v>46347</v>
+        <v>46345</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B70" s="1">
-        <v>46348</v>
+        <v>46346</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B71" s="1">
-        <v>46349</v>
+        <v>46347</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B72" s="1">
-        <v>46350</v>
+        <v>46348</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B73" s="1">
-        <v>46351</v>
+        <v>46349</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B74" s="1">
-        <v>46352</v>
+        <v>46350</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B75" s="1">
-        <v>46353</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B76" s="1">
-        <v>46354</v>
+        <v>46352</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B77" s="1">
-        <v>46355</v>
+        <v>46353</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B78" s="1">
-        <v>46356</v>
+        <v>46354</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B79" s="1">
-        <v>46357</v>
+        <v>46355</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B80" s="1">
-        <v>46358</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B81" s="1">
-        <v>46359</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B82" s="1">
-        <v>46360</v>
+        <v>46358</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B83" s="1">
-        <v>46361</v>
+        <v>46359</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B84" s="1">
-        <v>46362</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B85" s="1">
-        <v>46363</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B86" s="1">
-        <v>46364</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B87" s="1">
-        <v>46365</v>
+        <v>46363</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B88" s="1">
-        <v>46366</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B89" s="1">
-        <v>46367</v>
+        <v>46365</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B90" s="1">
-        <v>46368</v>
+        <v>46366</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B91" s="1">
-        <v>46369</v>
+        <v>46367</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B92" s="1">
-        <v>46370</v>
+        <v>46368</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B93" s="1">
-        <v>46371</v>
+        <v>46369</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B94" s="1">
-        <v>46372</v>
+        <v>46370</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B95" s="1">
-        <v>46373</v>
+        <v>46371</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B96" s="1">
-        <v>46374</v>
+        <v>46372</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B97" s="1">
-        <v>46375</v>
+        <v>46373</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B98" s="1">
-        <v>46376</v>
+        <v>46374</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B99" s="1">
-        <v>46377</v>
+        <v>46375</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B100" s="1">
-        <v>46378</v>
+        <v>46376</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B101" s="1">
-        <v>46379</v>
+        <v>46377</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B102" s="1">
-        <v>46380</v>
+        <v>46378</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B103" s="1">
-        <v>46381</v>
+        <v>46379</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B104" s="1">
-        <v>46382</v>
+        <v>46380</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B105" s="1">
-        <v>46383</v>
+        <v>46381</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B106" s="1">
-        <v>46384</v>
+        <v>46382</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B107" s="1">
-        <v>46385</v>
+        <v>46383</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B108" s="1">
-        <v>46386</v>
+        <v>46384</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B109" s="1">
-        <v>46387</v>
+        <v>46385</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B110" s="1">
-        <v>46388</v>
+        <v>46386</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B111" s="1">
-        <v>46389</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B112" s="1">
-        <v>46390</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B113" s="1">
-        <v>46391</v>
+        <v>46389</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B114" s="1">
-        <v>46392</v>
+        <v>46390</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B115" s="1">
-        <v>46393</v>
+        <v>46391</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B116" s="1">
-        <v>46394</v>
+        <v>46392</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B117" s="1">
-        <v>46395</v>
+        <v>46393</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B118" s="1">
-        <v>46396</v>
+        <v>46394</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B119" s="1">
-        <v>46397</v>
+        <v>46395</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B120" s="1">
-        <v>46398</v>
+        <v>46396</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B121" s="1">
-        <v>46399</v>
+        <v>46397</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B122" s="1">
-        <v>46400</v>
+        <v>46398</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B123" s="1">
-        <v>46401</v>
+        <v>46399</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B124" s="1">
-        <v>46402</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B125" s="1">
-        <v>46403</v>
+        <v>46401</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B126" s="1">
-        <v>46404</v>
+        <v>46402</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B127" s="1">
-        <v>46405</v>
+        <v>46403</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B128" s="1">
-        <v>46406</v>
+        <v>46404</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B129" s="1">
-        <v>46407</v>
+        <v>46405</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B130" s="1">
-        <v>46408</v>
+        <v>46406</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B131" s="1">
-        <v>46409</v>
+        <v>46407</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B132" s="1">
-        <v>46410</v>
+        <v>46408</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B133" s="1">
-        <v>46411</v>
+        <v>46409</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B134" s="1">
-        <v>46412</v>
+        <v>46410</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B135" s="1">
-        <v>46413</v>
+        <v>46411</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B136" s="1">
-        <v>46414</v>
+        <v>46412</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B137" s="1">
-        <v>46415</v>
+        <v>46413</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B138" s="1">
-        <v>46416</v>
+        <v>46414</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B139" s="1">
-        <v>46417</v>
+        <v>46415</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B140" s="1">
-        <v>46418</v>
+        <v>46416</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B141" s="1">
-        <v>46419</v>
+        <v>46417</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B142" s="1">
-        <v>46420</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B143" s="1">
-        <v>46421</v>
+        <v>46419</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B144" s="1">
-        <v>46422</v>
+        <v>46420</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B145" s="1">
-        <v>46423</v>
+        <v>46421</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B146" s="1">
-        <v>46424</v>
+        <v>46422</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B147" s="1">
-        <v>46425</v>
+        <v>46423</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B148" s="1">
-        <v>46426</v>
+        <v>46424</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B149" s="1">
-        <v>46427</v>
+        <v>46425</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B150" s="1">
-        <v>46428</v>
+        <v>46426</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B151" s="1">
-        <v>46429</v>
+        <v>46427</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B152" s="1">
-        <v>46430</v>
+        <v>46428</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B153" s="1">
-        <v>46431</v>
+        <v>46429</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B154" s="1">
-        <v>46432</v>
+        <v>46430</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B155" s="1">
-        <v>46433</v>
+        <v>46431</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B156" s="1">
-        <v>46434</v>
+        <v>46432</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B157" s="1">
-        <v>46435</v>
+        <v>46433</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B158" s="1">
-        <v>46436</v>
+        <v>46434</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B159" s="1">
-        <v>46437</v>
+        <v>46435</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B160" s="1">
-        <v>46438</v>
+        <v>46436</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B161" s="1">
-        <v>46439</v>
+        <v>46437</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B162" s="1">
-        <v>46440</v>
+        <v>46438</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B163" s="1">
-        <v>46441</v>
+        <v>46439</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B164" s="1">
-        <v>46442</v>
+        <v>46440</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B165" s="1">
-        <v>46443</v>
+        <v>46441</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B166" s="1">
-        <v>46444</v>
+        <v>46442</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B167" s="1">
-        <v>46445</v>
+        <v>46443</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B168" s="1">
-        <v>46446</v>
+        <v>46444</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B169" s="1">
-        <v>46447</v>
+        <v>46445</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B170" s="1">
-        <v>46448</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B171" s="1">
-        <v>46449</v>
+        <v>46447</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B172" s="1">
-        <v>46450</v>
+        <v>46448</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B173" s="1">
-        <v>46451</v>
+        <v>46449</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B174" s="1">
-        <v>46452</v>
+        <v>46450</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B175" s="1">
-        <v>46453</v>
+        <v>46451</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B176" s="1">
-        <v>46454</v>
+        <v>46452</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B177" s="1">
-        <v>46455</v>
+        <v>46453</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B178" s="1">
-        <v>46456</v>
+        <v>46454</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B179" s="1">
-        <v>46457</v>
+        <v>46455</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B180" s="1">
-        <v>46458</v>
+        <v>46456</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B181" s="1">
-        <v>46459</v>
+        <v>46457</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B182" s="1">
-        <v>46460</v>
+        <v>46458</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B183" s="1">
-        <v>46461</v>
+        <v>46459</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B184" s="1">
-        <v>46462</v>
+        <v>46460</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B185" s="1">
-        <v>46463</v>
+        <v>46461</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B186" s="1">
-        <v>46464</v>
+        <v>46462</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B187" s="1">
-        <v>46465</v>
+        <v>46463</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B188" s="1">
-        <v>46466</v>
+        <v>46464</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B189" s="1">
-        <v>46467</v>
+        <v>46465</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B190" s="1">
-        <v>46468</v>
+        <v>46466</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B191" s="1">
-        <v>46469</v>
+        <v>46467</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B192" s="1">
-        <v>46470</v>
+        <v>46468</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B193" s="1">
-        <v>46471</v>
+        <v>46469</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B194" s="1">
-        <v>46472</v>
+        <v>46470</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B195" s="1">
-        <v>46473</v>
+        <v>46471</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B196" s="1">
-        <v>46474</v>
+        <v>46472</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B197" s="1">
-        <v>46475</v>
+        <v>46473</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B198" s="1">
-        <v>46476</v>
+        <v>46474</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B199" s="1">
-        <v>46477</v>
+        <v>46475</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B200" s="1">
-        <v>46478</v>
+        <v>46476</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B201" s="1">
-        <v>46479</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B202" s="1">
-        <v>46480</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B203" s="1">
-        <v>46481</v>
+        <v>46479</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B204" s="1">
-        <v>46482</v>
+        <v>46480</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B205" s="1">
-        <v>46483</v>
+        <v>46481</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B206" s="1">
-        <v>46484</v>
+        <v>46482</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B207" s="1">
-        <v>46485</v>
+        <v>46483</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B208" s="1">
-        <v>46486</v>
+        <v>46484</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B209" s="1">
-        <v>46487</v>
+        <v>46485</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B210" s="1">
-        <v>46488</v>
+        <v>46486</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B211" s="1">
-        <v>46489</v>
+        <v>46487</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B212" s="1">
-        <v>46490</v>
+        <v>46488</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B213" s="1">
-        <v>46491</v>
+        <v>46489</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B214" s="1">
-        <v>46492</v>
+        <v>46490</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B215" s="1">
-        <v>46493</v>
+        <v>46491</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B216" s="1">
-        <v>46494</v>
+        <v>46492</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B217" s="1">
-        <v>46495</v>
+        <v>46493</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B218" s="1">
-        <v>46496</v>
+        <v>46494</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B219" s="1">
-        <v>46497</v>
+        <v>46495</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B220" s="1">
-        <v>46498</v>
+        <v>46496</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B221" s="1">
-        <v>46499</v>
+        <v>46497</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B222" s="1">
-        <v>46500</v>
+        <v>46498</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B223" s="1">
-        <v>46501</v>
+        <v>46499</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B224" s="1">
-        <v>46502</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B225" s="1">
-        <v>46503</v>
+        <v>46501</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B226" s="1">
-        <v>46504</v>
+        <v>46502</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B227" s="1">
-        <v>46505</v>
+        <v>46503</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B228" s="1">
-        <v>46506</v>
+        <v>46504</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B229" s="1">
-        <v>46507</v>
+        <v>46505</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B230" s="1">
-        <v>46508</v>
+        <v>46506</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B231" s="1">
-        <v>46509</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B232" s="1">
-        <v>46510</v>
+        <v>46508</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B233" s="1">
-        <v>46511</v>
+        <v>46509</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B234" s="1">
-        <v>46512</v>
+        <v>46510</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B235" s="1">
-        <v>46513</v>
+        <v>46511</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B236" s="1">
-        <v>46514</v>
+        <v>46512</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B237" s="1">
-        <v>46515</v>
+        <v>46513</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B238" s="1">
-        <v>46516</v>
+        <v>46514</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B239" s="1">
-        <v>46517</v>
+        <v>46515</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B240" s="1">
-        <v>46518</v>
+        <v>46516</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B241" s="1">
-        <v>46519</v>
+        <v>46517</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B242" s="1">
-        <v>46520</v>
+        <v>46518</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B243" s="1">
-        <v>46521</v>
+        <v>46519</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B244" s="1">
-        <v>46522</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B245" s="1">
-        <v>46523</v>
+        <v>46521</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B246" s="1">
-        <v>46524</v>
+        <v>46522</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B247" s="1">
-        <v>46525</v>
+        <v>46523</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B248" s="1">
-        <v>46526</v>
+        <v>46524</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B249" s="1">
-        <v>46527</v>
+        <v>46525</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B250" s="1">
-        <v>46528</v>
+        <v>46526</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B251" s="1">
-        <v>46529</v>
+        <v>46527</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B252" s="1">
-        <v>46530</v>
+        <v>46528</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B253" s="1">
-        <v>46531</v>
+        <v>46529</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B254" s="1">
-        <v>46532</v>
+        <v>46530</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B255" s="1">
-        <v>46533</v>
+        <v>46531</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B256" s="1">
-        <v>46534</v>
+        <v>46532</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B257" s="1">
-        <v>46535</v>
+        <v>46533</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B258" s="1">
-        <v>46536</v>
+        <v>46534</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B259" s="1">
-        <v>46537</v>
+        <v>46535</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B260" s="1">
-        <v>46538</v>
+        <v>46536</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B261" s="1">
-        <v>46539</v>
+        <v>46537</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B262" s="1">
-        <v>46540</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B263" s="1">
-        <v>46541</v>
+        <v>46539</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B264" s="1">
-        <v>46542</v>
+        <v>46540</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B265" s="1">
-        <v>46543</v>
+        <v>46541</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B266" s="1">
-        <v>46544</v>
+        <v>46542</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B267" s="1">
-        <v>46545</v>
+        <v>46543</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B268" s="1">
-        <v>46546</v>
+        <v>46544</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B269" s="1">
-        <v>46547</v>
+        <v>46545</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B270" s="1">
-        <v>46548</v>
+        <v>46546</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B271" s="1">
-        <v>46549</v>
+        <v>46547</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B272" s="1">
-        <v>46550</v>
+        <v>46548</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B273" s="1">
-        <v>46551</v>
+        <v>46549</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B274" s="1">
-        <v>46552</v>
+        <v>46550</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B275" s="1">
-        <v>46553</v>
+        <v>46551</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B276" s="1">
-        <v>46554</v>
+        <v>46552</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B277" s="1">
-        <v>46555</v>
+        <v>46553</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B278" s="1">
-        <v>46556</v>
+        <v>46554</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B279" s="1">
-        <v>46557</v>
+        <v>46555</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B280" s="1">
-        <v>46558</v>
+        <v>46556</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B281" s="1">
-        <v>46559</v>
+        <v>46557</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B282" s="1">
-        <v>46560</v>
+        <v>46558</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B283" s="1">
-        <v>46561</v>
+        <v>46559</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B284" s="1">
-        <v>46562</v>
+        <v>46560</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B285" s="1">
-        <v>46563</v>
+        <v>46561</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B286" s="1">
-        <v>46564</v>
+        <v>46562</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B287" s="1">
-        <v>46565</v>
+        <v>46563</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B288" s="1">
+        <v>46564</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>8</v>
+      </c>
+      <c r="B289" s="1">
+        <v>46565</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>2</v>
+      </c>
+      <c r="B290" s="1">
         <v>46566</v>
       </c>
     </row>
